--- a/बजेट माग estimate/thekka/लामाटोल खानेपानी ट्यांङ्की/लामाटोल खानेपानी ट्यांङ्की.xlsx
+++ b/बजेट माग estimate/thekka/लामाटोल खानेपानी ट्यांङ्की/लामाटोल खानेपानी ट्यांङ्की.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FDB6A4F-2D73-4D4A-8637-31C1B8BB17DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92141AC5-9464-4257-9D99-6C811BB45E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="71">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -259,9 +259,6 @@
   </si>
   <si>
     <t>-for binding shear wall of intake</t>
-  </si>
-  <si>
-    <t>Provisional sum for unforseen works</t>
   </si>
   <si>
     <r>
@@ -564,21 +561,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -600,6 +582,21 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1127,7 +1124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA91"/>
+  <dimension ref="A1:AA89"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="4" customWidth="1"/>
@@ -1145,113 +1142,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
     </row>
     <row r="2" spans="1:27" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
     </row>
     <row r="5" spans="1:27" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
     </row>
     <row r="6" spans="1:27" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="56" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
+      <c r="A6" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="57" t="s">
+      <c r="H6" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
     </row>
     <row r="7" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
       <c r="G7" s="6"/>
-      <c r="H7" s="51" t="s">
+      <c r="H7" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="51"/>
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
     </row>
     <row r="8" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
@@ -2738,7 +2735,7 @@
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="17"/>
       <c r="B74" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C74" s="19">
         <v>1</v>
@@ -2854,12 +2851,12 @@
       <c r="J79" s="19"/>
       <c r="K79" s="19"/>
     </row>
-    <row r="80" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="21">
         <v>11</v>
       </c>
       <c r="B80" s="33" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="C80" s="23">
         <v>1</v>
@@ -2875,11 +2872,11 @@
         <v>18</v>
       </c>
       <c r="I80" s="2">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="J80" s="25">
         <f>G80*I80</f>
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="K80" s="24"/>
     </row>
@@ -2896,156 +2893,120 @@
       <c r="J81" s="26"/>
       <c r="K81" s="24"/>
     </row>
-    <row r="82" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="21">
-        <v>12</v>
-      </c>
-      <c r="B82" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="C82" s="23">
-        <v>1</v>
-      </c>
-      <c r="D82" s="1"/>
-      <c r="E82" s="24"/>
-      <c r="F82" s="24"/>
-      <c r="G82" s="25">
-        <f>PRODUCT(C82:F82)</f>
-        <v>1</v>
-      </c>
-      <c r="H82" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I82" s="2">
-        <v>500</v>
-      </c>
-      <c r="J82" s="25">
-        <f>G82*I82</f>
-        <v>500</v>
-      </c>
-      <c r="K82" s="24"/>
+    <row r="82" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A82" s="35"/>
+      <c r="B82" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="C82" s="37"/>
+      <c r="D82" s="38"/>
+      <c r="E82" s="38"/>
+      <c r="F82" s="38"/>
+      <c r="G82" s="26"/>
+      <c r="H82" s="26"/>
+      <c r="I82" s="26"/>
+      <c r="J82" s="26">
+        <f>SUM(J10:J80)</f>
+        <v>405684.73727136286</v>
+      </c>
+      <c r="K82" s="39"/>
     </row>
     <row r="83" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A83" s="21"/>
-      <c r="B83" s="34"/>
-      <c r="C83" s="23"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="24"/>
-      <c r="F83" s="24"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="25"/>
-      <c r="I83" s="2"/>
-      <c r="J83" s="26"/>
-      <c r="K83" s="24"/>
-    </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A84" s="35"/>
-      <c r="B84" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="C84" s="37"/>
-      <c r="D84" s="38"/>
-      <c r="E84" s="38"/>
-      <c r="F84" s="38"/>
-      <c r="G84" s="26"/>
-      <c r="H84" s="26"/>
-      <c r="I84" s="26"/>
-      <c r="J84" s="26">
-        <f>SUM(J10:J82)</f>
-        <v>407684.73727136286</v>
-      </c>
-      <c r="K84" s="39"/>
+      <c r="AA83" s="11"/>
+    </row>
+    <row r="84" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="40"/>
+      <c r="B84" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C84" s="53">
+        <f>J82</f>
+        <v>405684.73727136286</v>
+      </c>
+      <c r="D84" s="54"/>
+      <c r="E84" s="32">
+        <v>100</v>
+      </c>
+      <c r="F84" s="40"/>
+      <c r="G84" s="41"/>
+      <c r="H84" s="40"/>
+      <c r="I84" s="42"/>
+      <c r="J84" s="43"/>
+      <c r="K84" s="44"/>
+      <c r="AA84" s="4"/>
     </row>
     <row r="85" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="AA85" s="11"/>
-    </row>
-    <row r="86" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="40"/>
+      <c r="B85" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C85" s="55">
+        <v>350000</v>
+      </c>
+      <c r="D85" s="56"/>
+      <c r="E85" s="32"/>
+    </row>
+    <row r="86" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B86" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C86" s="45">
-        <f>J84</f>
-        <v>407684.73727136286</v>
-      </c>
-      <c r="D86" s="46"/>
+        <v>22</v>
+      </c>
+      <c r="C86" s="55">
+        <f>C85-C88-C89</f>
+        <v>332500</v>
+      </c>
+      <c r="D86" s="56"/>
       <c r="E86" s="32">
-        <v>100</v>
-      </c>
-      <c r="F86" s="40"/>
-      <c r="G86" s="41"/>
-      <c r="H86" s="40"/>
-      <c r="I86" s="42"/>
-      <c r="J86" s="43"/>
-      <c r="K86" s="44"/>
-      <c r="AA86" s="4"/>
+        <f>C86/C84*100</f>
+        <v>81.960194567928852</v>
+      </c>
     </row>
     <row r="87" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B87" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="C87" s="47">
-        <v>350000</v>
-      </c>
-      <c r="D87" s="48"/>
-      <c r="E87" s="32"/>
+        <v>26</v>
+      </c>
+      <c r="C87" s="57">
+        <f>C84-C86</f>
+        <v>73184.737271362857</v>
+      </c>
+      <c r="D87" s="57"/>
+      <c r="E87" s="32">
+        <f>100-E86</f>
+        <v>18.039805432071148</v>
+      </c>
     </row>
     <row r="88" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B88" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="C88" s="47">
-        <f>C87-C90-C91</f>
-        <v>332500</v>
-      </c>
-      <c r="D88" s="48"/>
+        <v>23</v>
+      </c>
+      <c r="C88" s="53">
+        <f>C85*0.03</f>
+        <v>10500</v>
+      </c>
+      <c r="D88" s="54"/>
       <c r="E88" s="32">
-        <f>C88/C86*100</f>
-        <v>81.558118222777992</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B89" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="C89" s="49">
-        <f>C86-C88</f>
-        <v>75184.737271362857</v>
-      </c>
-      <c r="D89" s="49"/>
+        <v>24</v>
+      </c>
+      <c r="C89" s="53">
+        <f>C85*0.02</f>
+        <v>7000</v>
+      </c>
+      <c r="D89" s="54"/>
       <c r="E89" s="32">
-        <f>100-E88</f>
-        <v>18.441881777222008</v>
-      </c>
-    </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="B90" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="C90" s="45">
-        <f>C87*0.03</f>
-        <v>10500</v>
-      </c>
-      <c r="D90" s="46"/>
-      <c r="E90" s="32">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="B91" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="C91" s="45">
-        <f>C87*0.02</f>
-        <v>7000</v>
-      </c>
-      <c r="D91" s="46"/>
-      <c r="E91" s="32">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="C88:D88"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="H7:K7"/>
     <mergeCell ref="A1:K1"/>
@@ -3055,12 +3016,6 @@
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="C90:D90"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
